--- a/spec-tech/ig/StructureDefinition-xdmActorSystem.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdmActorSystem.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T14:32:10+00:00</t>
+    <t>2026-07-23T16:03:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-xdmActorSystem.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdmActorSystem.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T16:03:49+00:00</t>
+    <t>2026-07-23T16:11:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-xdmActorSystem.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdmActorSystem.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T16:11:23+00:00</t>
+    <t>2026-07-27T13:36:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-xdmActorSystem.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdmActorSystem.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="125">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T13:36:25+00:00</t>
+    <t>2026-07-30T09:32:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -108,7 +108,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/pdlgc/StructureDefinition/xdmActorXds|0.1.0</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/pdlgc/StructureDefinition/xdmActorXdsCore|0.1.0</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -262,33 +262,20 @@
     <t>1</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/fhir/pdlgc/StructureDefinition/xdmIdentifiant
+    <t xml:space="preserve">string {https://interop.esante.gouv.fr/ig/fhir/pdlgc/StructureDefinition/systIdNat|0.1.0}
 </t>
   </si>
   <si>
-    <t>Identifiant de l'acteur</t>
+    <t>Identifiant de l'acteur qui. Le format de l'identifiant doit respecter le datatype PatId, PSIdNat ou SystIdNat selon le type d'acteur</t>
   </si>
   <si>
     <t>3750100125/88</t>
   </si>
   <si>
-    <t>xdmActorXds.XCN1</t>
+    <t>xdmActorXdsCore.XCN1</t>
   </si>
   <si>
     <t>author/assignedAuthor/id@extension</t>
-  </si>
-  <si>
-    <t>xdmActorSystem.XCN1.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/fhir/pdlgc/StructureDefinition/systIdNat
-</t>
-  </si>
-  <si>
-    <t>Identifiant</t>
-  </si>
-  <si>
-    <t>xdmIdentifiant.value[x]</t>
   </si>
   <si>
     <t>xdmActorSystem.XCN2</t>
@@ -298,13 +285,13 @@
 </t>
   </si>
   <si>
-    <t>Nom du système</t>
+    <t>Nom et version du système</t>
   </si>
   <si>
     <t>Nom d'exercice du professionnel, nom du patient, nom du système.</t>
   </si>
   <si>
-    <t>xdmActorXds.XCN2</t>
+    <t>xdmActorXdsCore.XCN2</t>
   </si>
   <si>
     <t>author/assignedAuthor/assignedPerson/name/family</t>
@@ -319,7 +306,7 @@
     <t>Prénom usuel de la personne (par défaut le premier prénom), nom du modèle pour les dispositifs ou dénomination pour les autres systèmes.</t>
   </si>
   <si>
-    <t>xdmActorXds.XCN3</t>
+    <t>xdmActorXdsCore.XCN3</t>
   </si>
   <si>
     <t>author/assignedAuthor/assignedPerson/name/given</t>
@@ -335,7 +322,7 @@
     <t>Autorité d’affectation</t>
   </si>
   <si>
-    <t>xdmActorXds.XCN9</t>
+    <t>xdmActorXdsCore.XCN9</t>
   </si>
   <si>
     <t>NA</t>
@@ -347,7 +334,7 @@
     <t>Vide, pas de valeur</t>
   </si>
   <si>
-    <t>xdmActorXds.XCN9.composant1</t>
+    <t>xdmActorXdsCore.XCN9.composant1</t>
   </si>
   <si>
     <t>xdmActorSystem.XCN9.composant2</t>
@@ -359,7 +346,7 @@
     <t>1.2.250.1.71.4.2.1</t>
   </si>
   <si>
-    <t>xdmActorXds.XCN9.composant2</t>
+    <t>xdmActorXdsCore.XCN9.composant2</t>
   </si>
   <si>
     <t>author/assignedAuthor/id@root</t>
@@ -368,10 +355,13 @@
     <t>xdmActorSystem.XCN9.composant3</t>
   </si>
   <si>
-    <t>Valeur de Universal ID type (ID)</t>
-  </si>
-  <si>
-    <t>xdmActorXds.XCN9.composant3</t>
+    <t>Valeur de Universal ID type (ID). Valeur fixée à 'ISO'</t>
+  </si>
+  <si>
+    <t>ISO</t>
+  </si>
+  <si>
+    <t>xdmActorXdsCore.XCN9.composant3</t>
   </si>
   <si>
     <t>xdmActorSystem.XCN10</t>
@@ -381,13 +371,13 @@
 </t>
   </si>
   <si>
-    <t>Type de nom : Valeur en fonction de l’auteur :  D, pour les personnes physiques, -U, pour les systèmes.</t>
+    <t>Type de nom : 'D' pour les personnes physiques, 'U', pour les systèmes.</t>
   </si>
   <si>
     <t>U</t>
   </si>
   <si>
-    <t>xdmActorXds.XCN10</t>
+    <t>xdmActorXdsCore.XCN10</t>
   </si>
   <si>
     <t>xdmActorSystem.XCN13</t>
@@ -399,7 +389,7 @@
     <t>RI</t>
   </si>
   <si>
-    <t>xdmActorXds.XCN13</t>
+    <t>xdmActorXdsCore.XCN13</t>
   </si>
   <si>
     <t>Valeur ne provenant pas de l’en-tête CDA</t>
@@ -704,7 +694,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK12"/>
+  <dimension ref="A1:AK11"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="29.4375" customWidth="true" bestFit="true"/>
@@ -717,7 +707,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="61.53125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="68.96875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -738,7 +728,7 @@
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="26.47265625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="30.14453125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
@@ -1098,7 +1088,7 @@
         <v>89</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1149,7 +1139,7 @@
         <v>74</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>81</v>
@@ -1164,15 +1154,15 @@
         <v>74</v>
       </c>
       <c r="AK4" t="s" s="2">
-        <v>74</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1195,13 +1185,13 @@
         <v>74</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1252,7 +1242,7 @@
         <v>74</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>81</v>
@@ -1267,15 +1257,15 @@
         <v>74</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1298,13 +1288,13 @@
         <v>74</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1355,7 +1345,7 @@
         <v>74</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>81</v>
@@ -1370,15 +1360,15 @@
         <v>74</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1386,10 +1376,10 @@
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>74</v>
@@ -1401,7 +1391,7 @@
         <v>74</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="L7" t="s" s="2">
         <v>104</v>
@@ -1461,10 +1451,10 @@
         <v>105</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>74</v>
@@ -1473,15 +1463,15 @@
         <v>74</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1489,10 +1479,10 @@
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>74</v>
@@ -1504,13 +1494,13 @@
         <v>74</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1522,7 +1512,7 @@
         <v>74</v>
       </c>
       <c r="S8" t="s" s="2">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="T8" t="s" s="2">
         <v>74</v>
@@ -1564,10 +1554,10 @@
         <v>109</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>74</v>
@@ -1576,15 +1566,15 @@
         <v>74</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1607,13 +1597,13 @@
         <v>74</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1625,7 +1615,7 @@
         <v>74</v>
       </c>
       <c r="S9" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="T9" t="s" s="2">
         <v>74</v>
@@ -1664,7 +1654,7 @@
         <v>74</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>81</v>
@@ -1679,7 +1669,7 @@
         <v>74</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>114</v>
+        <v>102</v>
       </c>
     </row>
     <row r="10">
@@ -1710,13 +1700,13 @@
         <v>74</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>92</v>
+        <v>116</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1728,7 +1718,7 @@
         <v>74</v>
       </c>
       <c r="S10" t="s" s="2">
-        <v>74</v>
+        <v>118</v>
       </c>
       <c r="T10" t="s" s="2">
         <v>74</v>
@@ -1767,7 +1757,7 @@
         <v>74</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>81</v>
@@ -1782,15 +1772,15 @@
         <v>74</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1813,13 +1803,13 @@
         <v>74</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -1831,7 +1821,7 @@
         <v>74</v>
       </c>
       <c r="S11" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="T11" t="s" s="2">
         <v>74</v>
@@ -1870,7 +1860,7 @@
         <v>74</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>81</v>
@@ -1885,110 +1875,7 @@
         <v>74</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="C12" s="2"/>
-      <c r="D12" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E12" s="2"/>
-      <c r="F12" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G12" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H12" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I12" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J12" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K12" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="L12" t="s" s="2">
         <v>124</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="N12" s="2"/>
-      <c r="O12" s="2"/>
-      <c r="P12" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q12" s="2"/>
-      <c r="R12" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S12" t="s" s="2">
-        <v>125</v>
-      </c>
-      <c r="T12" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U12" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V12" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W12" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X12" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y12" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z12" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA12" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB12" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC12" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD12" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE12" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF12" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="AG12" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH12" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI12" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ12" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK12" t="s" s="2">
-        <v>127</v>
       </c>
     </row>
   </sheetData>

--- a/spec-tech/ig/StructureDefinition-xdmActorSystem.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdmActorSystem.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T09:32:03+00:00</t>
+    <t>2026-07-30T15:04:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-xdmActorSystem.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdmActorSystem.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T15:04:16+00:00</t>
+    <t>2026-08-07T08:28:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -256,7 +256,7 @@
     <t>ActorXDS</t>
   </si>
   <si>
-    <t>xdmActorSystem.XCN1</t>
+    <t>xdmActorSystem.xcn1</t>
   </si>
   <si>
     <t>1</t>
@@ -272,13 +272,13 @@
     <t>3750100125/88</t>
   </si>
   <si>
-    <t>xdmActorXdsCore.XCN1</t>
+    <t>xdmActorXdsCore.xcn1</t>
   </si>
   <si>
     <t>author/assignedAuthor/id@extension</t>
   </si>
   <si>
-    <t>xdmActorSystem.XCN2</t>
+    <t>xdmActorSystem.xcn2</t>
   </si>
   <si>
     <t xml:space="preserve">string
@@ -291,13 +291,13 @@
     <t>Nom d'exercice du professionnel, nom du patient, nom du système.</t>
   </si>
   <si>
-    <t>xdmActorXdsCore.XCN2</t>
+    <t>xdmActorXdsCore.xcn2</t>
   </si>
   <si>
     <t>author/assignedAuthor/assignedPerson/name/family</t>
   </si>
   <si>
-    <t>xdmActorSystem.XCN3</t>
+    <t>xdmActorSystem.xcn3</t>
   </si>
   <si>
     <t>Nom du modèle pour les dispositifs ou dénomination pour les autres systèmes.</t>
@@ -306,13 +306,13 @@
     <t>Prénom usuel de la personne (par défaut le premier prénom), nom du modèle pour les dispositifs ou dénomination pour les autres systèmes.</t>
   </si>
   <si>
-    <t>xdmActorXdsCore.XCN3</t>
+    <t>xdmActorXdsCore.xcn3</t>
   </si>
   <si>
     <t>author/assignedAuthor/assignedPerson/name/given</t>
   </si>
   <si>
-    <t>xdmActorSystem.XCN9</t>
+    <t>xdmActorSystem.xcn9</t>
   </si>
   <si>
     <t xml:space="preserve">Base
@@ -322,22 +322,22 @@
     <t>Autorité d’affectation</t>
   </si>
   <si>
-    <t>xdmActorXdsCore.XCN9</t>
+    <t>xdmActorXdsCore.xcn9</t>
   </si>
   <si>
     <t>NA</t>
   </si>
   <si>
-    <t>xdmActorSystem.XCN9.composant1</t>
+    <t>xdmActorSystem.xcn9.composant1</t>
   </si>
   <si>
     <t>Vide, pas de valeur</t>
   </si>
   <si>
-    <t>xdmActorXdsCore.XCN9.composant1</t>
-  </si>
-  <si>
-    <t>xdmActorSystem.XCN9.composant2</t>
+    <t>xdmActorXdsCore.xcn9.composant1</t>
+  </si>
+  <si>
+    <t>xdmActorSystem.xcn9.composant2</t>
   </si>
   <si>
     <t>Valeur de Universal ID</t>
@@ -346,13 +346,13 @@
     <t>1.2.250.1.71.4.2.1</t>
   </si>
   <si>
-    <t>xdmActorXdsCore.XCN9.composant2</t>
+    <t>xdmActorXdsCore.xcn9.composant2</t>
   </si>
   <si>
     <t>author/assignedAuthor/id@root</t>
   </si>
   <si>
-    <t>xdmActorSystem.XCN9.composant3</t>
+    <t>xdmActorSystem.xcn9.composant3</t>
   </si>
   <si>
     <t>Valeur de Universal ID type (ID). Valeur fixée à 'ISO'</t>
@@ -361,10 +361,10 @@
     <t>ISO</t>
   </si>
   <si>
-    <t>xdmActorXdsCore.XCN9.composant3</t>
-  </si>
-  <si>
-    <t>xdmActorSystem.XCN10</t>
+    <t>xdmActorXdsCore.xcn9.composant3</t>
+  </si>
+  <si>
+    <t>xdmActorSystem.xcn10</t>
   </si>
   <si>
     <t xml:space="preserve">code
@@ -377,10 +377,10 @@
     <t>U</t>
   </si>
   <si>
-    <t>xdmActorXdsCore.XCN10</t>
-  </si>
-  <si>
-    <t>xdmActorSystem.XCN13</t>
+    <t>xdmActorXdsCore.xcn10</t>
+  </si>
+  <si>
+    <t>xdmActorSystem.xcn13</t>
   </si>
   <si>
     <t>Type d’identifiant</t>
@@ -389,7 +389,7 @@
     <t>RI</t>
   </si>
   <si>
-    <t>xdmActorXdsCore.XCN13</t>
+    <t>xdmActorXdsCore.xcn13</t>
   </si>
   <si>
     <t>Valeur ne provenant pas de l’en-tête CDA</t>
@@ -697,8 +697,8 @@
   <dimension ref="A1:AK11"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="29.4375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="29.4375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="28.87890625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="28.87890625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -728,7 +728,7 @@
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="30.14453125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="29.58203125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
